--- a/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
+++ b/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4661DF3-6457-49C5-8C06-54BDDDD8BB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C02FAA7-C3A8-46BC-B832-60E71C39F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Joan of Arc" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="189">
   <si>
     <t>6 Villagers</t>
   </si>
@@ -3844,6 +3844,10 @@
   </si>
   <si>
     <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>Unavailable
+Careening and Clinker Construction start researched</t>
   </si>
 </sst>
 </file>
@@ -4381,6 +4385,18 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4397,18 +4413,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4753,7 +4757,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="49" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -5066,11 +5070,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5085,11 +5089,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
@@ -5126,15 +5130,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>180</v>
+      <c r="D5" s="46" t="s">
+        <v>188</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>88</v>
@@ -5150,8 +5154,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="17" t="s">
         <v>89</v>
@@ -5167,8 +5171,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="17" t="s">
         <v>90</v>
@@ -5184,8 +5188,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="17" t="s">
         <v>91</v>
@@ -5201,8 +5205,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="40" t="s">
         <v>92</v>
@@ -5218,8 +5222,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="18" t="s">
         <v>93</v>
@@ -5235,8 +5239,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="18" t="s">
         <v>94</v>
@@ -5252,8 +5256,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="18" t="s">
         <v>95</v>
@@ -5269,8 +5273,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="18" t="s">
         <v>98</v>
@@ -5286,8 +5290,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="17" t="s">
         <v>96</v>
@@ -5303,8 +5307,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="18" t="s">
         <v>99</v>
@@ -5320,8 +5324,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="19" t="s">
         <v>101</v>
@@ -5569,11 +5573,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5588,11 +5592,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="37" t="s">
         <v>133</v>
       </c>
@@ -5630,13 +5634,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>183</v>
       </c>
       <c r="G5" s="17" t="s">
@@ -5653,8 +5657,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="27" t="s">
         <v>135</v>
@@ -5670,8 +5674,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="18" t="s">
         <v>93</v>
@@ -5687,8 +5691,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="18" t="s">
         <v>95</v>
@@ -5704,8 +5708,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="18" t="s">
         <v>102</v>
@@ -5721,8 +5725,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="18" t="s">
         <v>88</v>
@@ -5738,8 +5742,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="18" t="s">
         <v>90</v>
@@ -5755,8 +5759,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="18" t="s">
         <v>91</v>
@@ -5772,8 +5776,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="18" t="s">
         <v>136</v>
@@ -5789,8 +5793,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="18" t="s">
         <v>98</v>
@@ -5806,8 +5810,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="21" t="s">
         <v>137</v>
@@ -5823,8 +5827,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="21" t="s">
         <v>94</v>
@@ -6044,11 +6048,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6063,11 +6067,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
@@ -6105,13 +6109,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>183</v>
       </c>
       <c r="G5" s="18" t="s">
@@ -6128,8 +6132,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="18" t="s">
         <v>88</v>
@@ -6145,8 +6149,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="18" t="s">
         <v>105</v>
@@ -6162,8 +6166,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="18" t="s">
         <v>136</v>
@@ -6179,8 +6183,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="18" t="s">
         <v>98</v>
@@ -6196,8 +6200,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="18" t="s">
         <v>94</v>
@@ -6213,8 +6217,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="21" t="s">
         <v>137</v>
@@ -6230,8 +6234,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="21" t="s">
         <v>102</v>
@@ -6247,8 +6251,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="21" t="s">
         <v>99</v>
@@ -6264,8 +6268,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="19" t="s">
         <v>91</v>
@@ -6281,8 +6285,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="19" t="s">
         <v>108</v>
@@ -6298,8 +6302,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="19" t="s">
         <v>138</v>
@@ -6523,11 +6527,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6542,11 +6546,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="33" t="s">
         <v>134</v>
       </c>
@@ -6584,13 +6588,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>186</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -6607,8 +6611,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="21" t="s">
         <v>88</v>
@@ -6624,8 +6628,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="21" t="s">
         <v>90</v>
@@ -6641,8 +6645,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="25" t="s">
         <v>135</v>
@@ -6658,8 +6662,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="25" t="s">
         <v>102</v>
@@ -6675,8 +6679,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="41" t="s">
         <v>105</v>
@@ -6692,8 +6696,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="25" t="s">
         <v>138</v>
@@ -6709,8 +6713,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="25" t="s">
         <v>108</v>
@@ -6726,8 +6730,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="25" t="s">
         <v>152</v>
@@ -6743,8 +6747,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="41" t="s">
         <v>153</v>
@@ -6760,8 +6764,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="25" t="s">
         <v>96</v>
@@ -6777,8 +6781,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="25" t="s">
         <v>99</v>
@@ -7040,11 +7044,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -7059,11 +7063,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="16" t="s">
         <v>87</v>
       </c>
@@ -7101,13 +7105,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>180</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -7124,8 +7128,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="21" t="s">
         <v>162</v>
@@ -7141,8 +7145,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="21" t="s">
         <v>110</v>
@@ -7158,8 +7162,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="21" t="s">
         <v>108</v>
@@ -7175,8 +7179,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="21" t="s">
         <v>101</v>
@@ -7192,8 +7196,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="21" t="s">
         <v>154</v>
@@ -7209,8 +7213,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="21" t="s">
         <v>155</v>
@@ -7226,8 +7230,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="21" t="s">
         <v>103</v>
@@ -7243,8 +7247,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="21" t="s">
         <v>164</v>
@@ -7260,8 +7264,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="21" t="s">
         <v>165</v>
@@ -7277,8 +7281,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="18" t="s">
         <v>152</v>
@@ -7294,8 +7298,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="40" t="s">
         <v>167</v>
@@ -7531,11 +7535,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -7550,11 +7554,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="31" t="s">
         <v>135</v>
       </c>
@@ -7592,13 +7596,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>186</v>
       </c>
       <c r="G5" s="18" t="s">
@@ -7615,8 +7619,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="G6" s="18" t="s">
         <v>93</v>
@@ -7632,8 +7636,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="15"/>
       <c r="G7" s="18" t="s">
         <v>95</v>
@@ -7649,8 +7653,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="15"/>
       <c r="G8" s="18" t="s">
         <v>103</v>
@@ -7666,8 +7670,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="15"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
@@ -7683,8 +7687,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="15"/>
       <c r="G10" s="18" t="s">
         <v>173</v>
@@ -7700,8 +7704,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="15"/>
       <c r="G11" s="18" t="s">
         <v>101</v>
@@ -7717,8 +7721,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="15"/>
       <c r="G12" s="40" t="s">
         <v>174</v>
@@ -7734,8 +7738,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="15"/>
       <c r="G13" s="18" t="s">
         <v>161</v>
@@ -7751,8 +7755,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="15"/>
       <c r="G14" s="18" t="s">
         <v>162</v>
@@ -7768,8 +7772,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="15"/>
       <c r="G15" s="19" t="s">
         <v>108</v>
@@ -7785,8 +7789,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="15"/>
       <c r="G16" s="19" t="s">
         <v>96</v>

--- a/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
+++ b/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C02FAA7-C3A8-46BC-B832-60E71C39F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0576D9B1-3DA8-4BCA-B753-F9D7A712814F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Joan of Arc" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="212">
   <si>
     <t>6 Villagers</t>
   </si>
@@ -3848,6 +3848,75 @@
   <si>
     <t>Unavailable
 Careening and Clinker Construction start researched</t>
+  </si>
+  <si>
+    <t>Franks</t>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Joan the Maid</t>
+  </si>
+  <si>
+    <t>Sieur Bertrand</t>
+  </si>
+  <si>
+    <t>Sieur de Metz</t>
+  </si>
+  <si>
+    <t>Joan of Arc</t>
+  </si>
+  <si>
+    <t>Duke D'Alencon</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Enough Houses</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>La Hire</t>
+  </si>
+  <si>
+    <t>Lord de Graville</t>
+  </si>
+  <si>
+    <t>Jean de Lorrain</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Cart carrying the French flag</t>
+  </si>
+  <si>
+    <t>Guy Josselyne</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Constable Richemont</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Jean Bureau</t>
   </si>
 </sst>
 </file>
@@ -4084,7 +4153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -4244,11 +4313,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4391,9 +4504,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4413,6 +4523,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4757,7 +4888,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="48" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -5064,17 +5195,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5089,11 +5221,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
@@ -5108,15 +5240,11 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B4" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="54"/>
       <c r="G4" s="2" t="s">
         <v>87</v>
       </c>
@@ -5130,15 +5258,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>188</v>
+    <row r="5" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>88</v>
@@ -5153,10 +5281,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="15"/>
+    <row r="6" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>188</v>
+      </c>
       <c r="G6" s="17" t="s">
         <v>89</v>
       </c>
@@ -5170,7 +5304,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -5187,10 +5321,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="17" t="s">
         <v>91</v>
       </c>
@@ -5205,9 +5348,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="57"/>
       <c r="G9" s="40" t="s">
         <v>92</v>
       </c>
@@ -5222,9 +5370,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="57"/>
       <c r="G10" s="18" t="s">
         <v>93</v>
       </c>
@@ -5239,9 +5392,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="57"/>
       <c r="G11" s="18" t="s">
         <v>94</v>
       </c>
@@ -5256,9 +5414,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="57"/>
       <c r="G12" s="18" t="s">
         <v>95</v>
       </c>
@@ -5273,9 +5434,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="57"/>
       <c r="G13" s="18" t="s">
         <v>98</v>
       </c>
@@ -5290,9 +5454,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="57"/>
       <c r="G14" s="17" t="s">
         <v>96</v>
       </c>
@@ -5307,9 +5474,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="57"/>
       <c r="G15" s="18" t="s">
         <v>99</v>
       </c>
@@ -5324,9 +5494,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="57"/>
       <c r="G16" s="19" t="s">
         <v>101</v>
       </c>
@@ -5340,7 +5513,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="19" t="s">
         <v>102</v>
       </c>
@@ -5354,7 +5531,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="17" t="s">
         <v>103</v>
       </c>
@@ -5368,7 +5549,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="20" t="s">
         <v>104</v>
       </c>
@@ -5382,7 +5567,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="17" t="s">
         <v>105</v>
       </c>
@@ -5396,7 +5585,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="21" t="s">
         <v>108</v>
       </c>
@@ -5410,7 +5603,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
       <c r="G22" s="22" t="s">
         <v>109</v>
       </c>
@@ -5424,7 +5617,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
       <c r="G23" s="22" t="s">
         <v>110</v>
       </c>
@@ -5438,55 +5631,55 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
@@ -5553,11 +5746,13 @@
       <c r="L42" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5567,17 +5762,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5592,11 +5788,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="37" t="s">
         <v>133</v>
       </c>
@@ -5673,7 +5869,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -5690,10 +5886,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="18" t="s">
         <v>95</v>
       </c>
@@ -5708,9 +5913,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>117</v>
+      </c>
       <c r="G9" s="18" t="s">
         <v>102</v>
       </c>
@@ -5725,9 +5937,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>118</v>
+      </c>
       <c r="G10" s="18" t="s">
         <v>88</v>
       </c>
@@ -5741,10 +5960,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>125</v>
+      </c>
       <c r="G11" s="18" t="s">
         <v>90</v>
       </c>
@@ -5759,9 +5985,16 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>200</v>
+      </c>
       <c r="G12" s="18" t="s">
         <v>91</v>
       </c>
@@ -5776,9 +6009,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58" t="s">
+        <v>122</v>
+      </c>
       <c r="G13" s="18" t="s">
         <v>136</v>
       </c>
@@ -5793,9 +6031,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="56" t="s">
+        <v>115</v>
+      </c>
       <c r="G14" s="18" t="s">
         <v>98</v>
       </c>
@@ -5810,9 +6051,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="56" t="s">
+        <v>121</v>
+      </c>
       <c r="G15" s="21" t="s">
         <v>137</v>
       </c>
@@ -5827,9 +6071,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="56" t="s">
+        <v>140</v>
+      </c>
       <c r="G16" s="21" t="s">
         <v>94</v>
       </c>
@@ -5843,7 +6090,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="56" t="s">
+        <v>124</v>
+      </c>
       <c r="G17" s="26" t="s">
         <v>138</v>
       </c>
@@ -5857,7 +6110,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="56" t="s">
+        <v>118</v>
+      </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="K18" s="18" t="s">
@@ -5867,7 +6126,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="46" t="s">
+        <v>141</v>
+      </c>
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="K19" s="19" t="s">
@@ -5877,7 +6142,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="K20" s="19" t="s">
@@ -5887,7 +6156,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="K21" s="22" t="s">
@@ -5897,7 +6170,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="K22" s="29" t="s">
@@ -5907,61 +6180,61 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
@@ -6041,18 +6314,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6067,11 +6340,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
@@ -6148,7 +6421,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -6165,10 +6438,19 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="18" t="s">
         <v>136</v>
       </c>
@@ -6183,9 +6465,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="57"/>
       <c r="G9" s="18" t="s">
         <v>98</v>
       </c>
@@ -6200,9 +6487,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="57"/>
       <c r="G10" s="18" t="s">
         <v>94</v>
       </c>
@@ -6217,9 +6509,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
       <c r="G11" s="21" t="s">
         <v>137</v>
       </c>
@@ -6234,9 +6529,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
       <c r="G12" s="21" t="s">
         <v>102</v>
       </c>
@@ -6251,9 +6549,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
       <c r="G13" s="21" t="s">
         <v>99</v>
       </c>
@@ -6268,9 +6569,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
       <c r="G14" s="19" t="s">
         <v>91</v>
       </c>
@@ -6285,9 +6589,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
       <c r="G15" s="19" t="s">
         <v>108</v>
       </c>
@@ -6302,9 +6609,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="G16" s="19" t="s">
         <v>138</v>
       </c>
@@ -6318,7 +6626,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="19" t="s">
         <v>96</v>
       </c>
@@ -6332,7 +6644,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="30" t="s">
         <v>148</v>
       </c>
@@ -6346,7 +6662,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="K19" s="21" t="s">
@@ -6356,7 +6676,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="K20" s="21" t="s">
@@ -6366,7 +6690,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="K21" s="21" t="s">
@@ -6376,7 +6704,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="K22" s="44" t="s">
@@ -6386,61 +6714,61 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
@@ -6521,17 +6849,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6546,11 +6875,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="33" t="s">
         <v>134</v>
       </c>
@@ -6627,7 +6956,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -6644,10 +6973,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="25" t="s">
         <v>135</v>
       </c>
@@ -6662,9 +7000,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>117</v>
+      </c>
       <c r="G9" s="25" t="s">
         <v>102</v>
       </c>
@@ -6679,9 +7024,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="56" t="s">
+        <v>142</v>
+      </c>
       <c r="G10" s="41" t="s">
         <v>105</v>
       </c>
@@ -6696,9 +7046,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="56" t="s">
+        <v>118</v>
+      </c>
       <c r="G11" s="25" t="s">
         <v>138</v>
       </c>
@@ -6713,9 +7068,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="46" t="s">
+        <v>141</v>
+      </c>
       <c r="G12" s="25" t="s">
         <v>108</v>
       </c>
@@ -6730,9 +7090,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
       <c r="G13" s="25" t="s">
         <v>152</v>
       </c>
@@ -6747,9 +7110,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
       <c r="G14" s="41" t="s">
         <v>153</v>
       </c>
@@ -6764,9 +7130,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
       <c r="G15" s="25" t="s">
         <v>96</v>
       </c>
@@ -6781,9 +7148,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="G16" s="25" t="s">
         <v>99</v>
       </c>
@@ -6797,7 +7165,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="25" t="s">
         <v>154</v>
       </c>
@@ -6811,7 +7183,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="25" t="s">
         <v>155</v>
       </c>
@@ -6825,7 +7201,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="41" t="s">
         <v>156</v>
       </c>
@@ -6839,7 +7219,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="19" t="s">
         <v>89</v>
       </c>
@@ -6853,7 +7237,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="19" t="s">
         <v>98</v>
       </c>
@@ -6867,7 +7255,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="17" t="s">
         <v>137</v>
       </c>
@@ -6881,7 +7269,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="17" t="s">
         <v>110</v>
       </c>
@@ -6891,7 +7279,7 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="17" t="s">
         <v>101</v>
       </c>
@@ -6901,7 +7289,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="17" t="s">
         <v>94</v>
       </c>
@@ -6911,7 +7299,7 @@
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="35" t="s">
         <v>109</v>
       </c>
@@ -6921,7 +7309,7 @@
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="19" t="s">
         <v>158</v>
       </c>
@@ -6931,7 +7319,7 @@
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="41" t="s">
         <v>157</v>
       </c>
@@ -6941,23 +7329,23 @@
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
@@ -7038,17 +7426,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -7063,11 +7452,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="16" t="s">
         <v>87</v>
       </c>
@@ -7144,7 +7533,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -7161,10 +7550,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="21" t="s">
         <v>108</v>
       </c>
@@ -7179,9 +7577,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="57"/>
       <c r="G9" s="21" t="s">
         <v>101</v>
       </c>
@@ -7196,9 +7599,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="57"/>
       <c r="G10" s="21" t="s">
         <v>154</v>
       </c>
@@ -7213,9 +7621,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="57"/>
       <c r="G11" s="21" t="s">
         <v>155</v>
       </c>
@@ -7230,9 +7643,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="57"/>
       <c r="G12" s="21" t="s">
         <v>103</v>
       </c>
@@ -7247,9 +7665,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="57"/>
       <c r="G13" s="21" t="s">
         <v>164</v>
       </c>
@@ -7264,9 +7687,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="57"/>
       <c r="G14" s="21" t="s">
         <v>165</v>
       </c>
@@ -7281,9 +7709,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="57"/>
       <c r="G15" s="18" t="s">
         <v>152</v>
       </c>
@@ -7298,9 +7731,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
       <c r="G16" s="40" t="s">
         <v>167</v>
       </c>
@@ -7314,7 +7750,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="G17" s="40" t="s">
         <v>168</v>
       </c>
@@ -7328,7 +7770,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="G18" s="18" t="s">
         <v>109</v>
       </c>
@@ -7342,7 +7790,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
       <c r="G19" s="40" t="s">
         <v>169</v>
       </c>
@@ -7356,7 +7808,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
       <c r="G20" s="27" t="s">
         <v>90</v>
       </c>
@@ -7370,7 +7826,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="17" t="s">
         <v>157</v>
       </c>
@@ -7384,7 +7844,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="K22" s="22" t="s">
@@ -7394,61 +7854,61 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
@@ -7529,17 +7989,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -7554,11 +8015,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="31" t="s">
         <v>135</v>
       </c>
@@ -7635,7 +8096,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="15"/>
@@ -7652,10 +8113,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="15"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="18" t="s">
         <v>103</v>
       </c>
@@ -7669,10 +8139,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="15"/>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="57"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
@@ -7687,9 +8162,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="57"/>
       <c r="G10" s="18" t="s">
         <v>173</v>
       </c>
@@ -7704,9 +8184,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" s="57"/>
       <c r="G11" s="18" t="s">
         <v>101</v>
       </c>
@@ -7721,9 +8204,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="57"/>
       <c r="G12" s="40" t="s">
         <v>174</v>
       </c>
@@ -7738,9 +8224,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="57"/>
       <c r="G13" s="18" t="s">
         <v>161</v>
       </c>
@@ -7755,9 +8244,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="57"/>
       <c r="G14" s="18" t="s">
         <v>162</v>
       </c>
@@ -7772,9 +8264,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="57"/>
       <c r="G15" s="19" t="s">
         <v>108</v>
       </c>
@@ -7788,10 +8283,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="15"/>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="57"/>
       <c r="G16" s="19" t="s">
         <v>96</v>
       </c>
@@ -7805,7 +8303,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="57"/>
       <c r="G17" s="21" t="s">
         <v>102</v>
       </c>
@@ -7819,7 +8323,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="57"/>
       <c r="G18" s="21" t="s">
         <v>137</v>
       </c>
@@ -7833,7 +8343,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="57"/>
       <c r="G19" s="21" t="s">
         <v>154</v>
       </c>
@@ -7847,7 +8363,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="57"/>
       <c r="G20" s="21" t="s">
         <v>155</v>
       </c>
@@ -7861,7 +8383,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="G21" s="21" t="s">
         <v>110</v>
       </c>
@@ -7875,7 +8401,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="36" t="s">
         <v>164</v>
       </c>
@@ -7889,61 +8415,61 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="K32" s="23"/>
